--- a/data/trans_bre/IP1020-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP1020-Edad-trans_bre.xlsx
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,08; -0,56</t>
+          <t>-5,61; -0,56</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,49; 7,0</t>
+          <t>0,45; 6,63</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,8; 1,64</t>
+          <t>-3,74; 1,45</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,82; 8,94</t>
+          <t>0,8; 8,84</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,7 +685,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-50,46; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -760,22 +760,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 1,52</t>
+          <t>-1,01; 1,55</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 4,65</t>
+          <t>-0,38; 4,87</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 1,69</t>
+          <t>-1,99; 1,86</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-4,25; 2,67</t>
+          <t>-5,07; 2,57</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -785,17 +785,17 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-23,2; 430,07</t>
+          <t>-26,44; 427,99</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-81,56; 275,09</t>
+          <t>-78,95; 267,95</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-68,49; 119,41</t>
+          <t>-71,67; 103,73</t>
         </is>
       </c>
     </row>
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,03</t>
+          <t>0,0; 4,77</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 1,58</t>
+          <t>-3,34; 1,24</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 1,52</t>
+          <t>-2,83; 1,31</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,44; 3,05</t>
+          <t>-4,61; 2,7</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 577,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-67,34; 125,05</t>
+          <t>-71,99; 103,86</t>
         </is>
       </c>
     </row>
@@ -960,22 +960,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 1,24</t>
+          <t>-1,63; 1,29</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 1,79</t>
+          <t>-1,3; 1,52</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 1,62</t>
+          <t>-2,43; 1,57</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 3,55</t>
+          <t>-1,15; 3,7</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 560,81</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-46,32; 379,21</t>
+          <t>-46,91; 417,7</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 0,78</t>
+          <t>-0,92; 0,66</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,1; 2,48</t>
+          <t>-0,04; 2,44</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 0,6</t>
+          <t>-1,62; 0,57</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 1,88</t>
+          <t>-1,46; 1,79</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-72,25; 158,21</t>
+          <t>-72,36; 143,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,58; 292,55</t>
+          <t>-10,34; 274,72</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-62,44; 61,85</t>
+          <t>-65,28; 51,53</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-36,46; 76,63</t>
+          <t>-37,27; 70,28</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP1020-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP1020-Edad-trans_bre.xlsx
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,61; -0,56</t>
+          <t>-5,1; -0,56</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,45; 6,63</t>
+          <t>0,56; 6,59</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 1,45</t>
+          <t>-3,67; 1,5</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,8; 8,84</t>
+          <t>0,81; 8,82</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,7 +685,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-50,46; —</t>
+          <t>-20,62; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -760,22 +760,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 1,55</t>
+          <t>-0,92; 1,7</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 4,87</t>
+          <t>-0,5; 4,96</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 1,86</t>
+          <t>-1,81; 1,86</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-5,07; 2,57</t>
+          <t>-4,76; 2,29</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -785,17 +785,17 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-26,44; 427,99</t>
+          <t>-24,26; 500,61</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-78,95; 267,95</t>
+          <t>-71,61; 325,37</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-71,67; 103,73</t>
+          <t>-72,04; 93,0</t>
         </is>
       </c>
     </row>
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,77</t>
+          <t>0,0; 3,89</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,34; 1,24</t>
+          <t>-3,14; 1,51</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,83; 1,31</t>
+          <t>-3,14; 1,25</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,61; 2,7</t>
+          <t>-4,68; 2,73</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 236,14</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-71,99; 103,86</t>
+          <t>-68,77; 95,4</t>
         </is>
       </c>
     </row>
@@ -960,22 +960,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 1,29</t>
+          <t>-1,55; 1,24</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 1,52</t>
+          <t>-0,92; 1,82</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 1,57</t>
+          <t>-2,73; 1,48</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 3,7</t>
+          <t>-1,08; 3,81</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 310,15</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-46,91; 417,7</t>
+          <t>-47,47; 368,39</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 0,66</t>
+          <t>-0,81; 0,69</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,04; 2,44</t>
+          <t>-0,04; 2,55</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 0,57</t>
+          <t>-1,44; 0,65</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 1,79</t>
+          <t>-1,59; 1,84</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-72,36; 143,0</t>
+          <t>-70,82; 135,01</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-10,34; 274,72</t>
+          <t>-8,61; 260,56</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-65,28; 51,53</t>
+          <t>-63,25; 55,88</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-37,27; 70,28</t>
+          <t>-41,21; 67,9</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP1020-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP1020-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3,11</t>
+          <t>3,45</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,1; -0,56</t>
+          <t>-5,08; -0,56</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,56; 6,59</t>
+          <t>0,49; 7,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,67; 1,5</t>
+          <t>-3,8; 1,64</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,81; 8,82</t>
+          <t>0,94; 9,41</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,7 +685,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-20,62; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-1,2</t>
+          <t>-1,18</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-24,83%</t>
+          <t>-23,34%</t>
         </is>
       </c>
     </row>
@@ -760,22 +760,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 1,7</t>
+          <t>-0,98; 1,52</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 4,96</t>
+          <t>-0,35; 4,65</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 1,86</t>
+          <t>-2,09; 1,69</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-4,76; 2,29</t>
+          <t>-4,66; 3,01</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -785,17 +785,17 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-24,26; 500,61</t>
+          <t>-23,2; 430,07</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-71,61; 325,37</t>
+          <t>-81,56; 275,09</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-72,04; 93,0</t>
+          <t>-69,03; 121,12</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-0,96</t>
+          <t>-0,94</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-20,15%</t>
+          <t>-19,07%</t>
         </is>
       </c>
     </row>
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,89</t>
+          <t>0,0; 4,03</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 1,51</t>
+          <t>-3,06; 1,58</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 1,25</t>
+          <t>-2,69; 1,52</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,68; 2,73</t>
+          <t>-4,5; 3,16</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -885,17 +885,17 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
+          <t>-100,0; 577,08</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 236,14</t>
-        </is>
-      </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-68,77; 95,4</t>
+          <t>-67,31; 126,23</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1,06</t>
+          <t>1,31</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>56,13%</t>
+          <t>62,58%</t>
         </is>
       </c>
     </row>
@@ -960,22 +960,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 1,24</t>
+          <t>-1,49; 1,24</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 1,82</t>
+          <t>-0,9; 1,79</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 1,48</t>
+          <t>-2,38; 1,62</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 3,81</t>
+          <t>-1,02; 4,1</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 310,15</t>
+          <t>-100,0; 560,81</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-47,47; 368,39</t>
+          <t>-42,11; 407,14</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,11</t>
+          <t>0,26</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>7,7%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 0,69</t>
+          <t>-0,89; 0,78</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,04; 2,55</t>
+          <t>0,1; 2,48</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 0,65</t>
+          <t>-1,34; 0,6</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 1,84</t>
+          <t>-1,34; 2,13</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-70,82; 135,01</t>
+          <t>-72,25; 158,21</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-8,61; 260,56</t>
+          <t>2,58; 292,55</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-63,25; 55,88</t>
+          <t>-62,44; 61,85</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-41,21; 67,9</t>
+          <t>-33,66; 82,75</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP1020-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP1020-Edad-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,44 +619,30 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>-2,24</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>3,02</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-0,74</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3,45</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>338,47%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-35,04%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
+      <c r="C4" s="5" t="n">
+        <v>-2.241484891836017</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>3.016501011399221</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-0.7350372157209359</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>3.454631284303485</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>3.384678632297281</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>-0.3504451388796321</v>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
         </is>
       </c>
     </row>
@@ -655,254 +650,150 @@
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-5,08; -0,56</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>0,49; 7,0</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-3,8; 1,64</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>0,94; 9,41</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-5.080016650980039</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.4936508753278455</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-3.797899839463771</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>0.9383046770360837</v>
+      </c>
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr"/>
+      <c r="I5" s="6" t="inlineStr"/>
+      <c r="J5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>-0.5550440292011772</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>6.998152871416159</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>1.637197179060737</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>9.411716240426907</v>
+      </c>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr"/>
+      <c r="I6" s="6" t="inlineStr"/>
+      <c r="J6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>3-7</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>0,27</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>1,95</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-0,06</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-1,18</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>36,42%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>94,2%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-3,73%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-23,34%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-0,98; 1,52</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-0,35; 4,65</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-2,09; 1,69</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-4,66; 3,01</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-23,2; 430,07</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-81,56; 275,09</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-69,03; 121,12</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>0.2712521586618123</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>1.945320923878116</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-0.06081353242053771</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-1.178944983370573</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.3641851518395803</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0.9420234064516274</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>-0.03729681122098177</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-0.2333721050185159</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>1,13</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-0,61</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-0,55</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-0,94</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-33,49%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-32,68%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-19,07%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-0.9804781883692064</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-0.3541948300162502</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-2.086523187146987</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-4.657721276679959</v>
+      </c>
+      <c r="G8" s="6" t="inlineStr"/>
+      <c r="H8" s="6" t="n">
+        <v>-0.2319880031295153</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.8155836921181499</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.6902961116732109</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 4,03</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-3,06; 1,58</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-2,69; 1,52</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-4,5; 3,16</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 577,08</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-67,31; 126,23</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>1.517655612000067</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>4.654990460247359</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>1.690114951229469</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>3.006492190741028</v>
+      </c>
+      <c r="G9" s="6" t="inlineStr"/>
+      <c r="H9" s="6" t="n">
+        <v>4.300653982206814</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>2.750929492616269</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>1.211205193489805</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>12-15</t>
+          <t>8-11</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,197 +801,283 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-0,19</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>0,31</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-0,39</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1,31</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-20,76%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>72,53%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>-24,96%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>62,58%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>1.128528959953066</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-0.6131337825085093</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-0.5455232857863136</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-0.9352176771898695</v>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-0.3349463281983316</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>-0.3267520032209697</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>-0.1907055534703109</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-1,49; 1,24</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-0,9; 1,79</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-2,38; 1,62</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-1,02; 4,1</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 560,81</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-42,11; 407,14</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-3.056651944540069</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-2.694740270873369</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-4.504292138149565</v>
+      </c>
+      <c r="G11" s="6" t="inlineStr"/>
+      <c r="H11" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I11" s="6" t="inlineStr"/>
+      <c r="J11" s="6" t="n">
+        <v>-0.6731367261388171</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>4.029394957711887</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>1.577100418473737</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>1.524371974077981</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>3.162401524641325</v>
+      </c>
+      <c r="G12" s="6" t="inlineStr"/>
+      <c r="H12" s="6" t="n">
+        <v>5.770825290762074</v>
+      </c>
+      <c r="I12" s="6" t="inlineStr"/>
+      <c r="J12" s="6" t="n">
+        <v>1.262270629162713</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>-0.1856576721732032</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.3124155831395594</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-0.3936819687188197</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>1.307461563119537</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.2076395118399801</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0.7252712271616423</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>-0.249595539700108</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>0.6257934122234607</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-1.49008100241787</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-0.9046690287735024</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-2.384357096792885</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-1.020146198086696</v>
+      </c>
+      <c r="G14" s="6" t="inlineStr"/>
+      <c r="H14" s="6" t="inlineStr"/>
+      <c r="I14" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.4210805816173525</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>1.241162240517156</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>1.78538369239707</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>1.62415706989793</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>4.099065205277981</v>
+      </c>
+      <c r="G15" s="6" t="inlineStr"/>
+      <c r="H15" s="6" t="inlineStr"/>
+      <c r="I15" s="6" t="n">
+        <v>5.608090118342679</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>4.071396843226835</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>-0,1</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>1,19</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-0,39</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,26</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-11,41%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>84,7%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>-22,83%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>7,7%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-0,89; 0,78</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>0,1; 2,48</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-1,34; 0,6</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-1,34; 2,13</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-72,25; 158,21</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>2,58; 292,55</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-62,44; 61,85</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-33,66; 82,75</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>-0.101853594215468</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>1.185675628875601</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-0.3893560508871737</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>0.2623625142241598</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>-0.1140687109129268</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>0.8469948233721764</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>-0.2282550770948683</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>0.07697880987389308</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-0.888422891794196</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0.09830693653064784</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-1.337781079538165</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-1.337616091093948</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.7225377146048392</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>0.02584947365055118</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.6243521772745275</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-0.3366003518646223</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.7763657359455322</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>2.478408442990316</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.6014174259371712</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>2.133175765455143</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>1.582116715665239</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>2.925490288239466</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>0.6185422157354691</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>0.8275260690864957</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1108,14 +1085,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
